--- a/output/full_scan/batch_seq1_2026-09-08.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-08.xlsx
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>189.4944686881038</v>
+        <v>189.4944686881037</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>15.3</v>
